--- a/artfynd/A 73144-2021 artfynd.xlsx
+++ b/artfynd/A 73144-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73144-2021 artfynd.xlsx
+++ b/artfynd/A 73144-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1046,6 +1046,131 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127888821</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56585</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lantmannavägen, 623 65 Ljugarn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>722296</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6360820</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 73144-2021 artfynd.xlsx
+++ b/artfynd/A 73144-2021 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>127888821</v>
       </c>
       <c r="B5" t="n">
-        <v>56585</v>
+        <v>56612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 73144-2021 artfynd.xlsx
+++ b/artfynd/A 73144-2021 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>127888821</v>
       </c>
       <c r="B5" t="n">
-        <v>56612</v>
+        <v>56615</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 73144-2021 artfynd.xlsx
+++ b/artfynd/A 73144-2021 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>127888821</v>
       </c>
       <c r="B5" t="n">
-        <v>56615</v>
+        <v>56618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 73144-2021 artfynd.xlsx
+++ b/artfynd/A 73144-2021 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>127888821</v>
       </c>
       <c r="B5" t="n">
-        <v>56618</v>
+        <v>56620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 73144-2021 artfynd.xlsx
+++ b/artfynd/A 73144-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96511035</v>
+        <v>96486085</v>
       </c>
       <c r="B2" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>424</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lauritse, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>722263.5924197305</v>
+        <v>722265</v>
       </c>
       <c r="R2" t="n">
-        <v>6360984.120605819</v>
+        <v>6361049</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,7 +736,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Ardre</t>
+          <t>Alskog</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -748,26 +744,11 @@
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Minst 50 plantor</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -776,40 +757,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Michael Krikorev</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97694548</v>
+        <v>96511036</v>
       </c>
       <c r="B3" t="n">
-        <v>97822</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,41 +784,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>783</v>
+        <v>424</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>722275.2864490182</v>
+        <v>722265</v>
       </c>
       <c r="R3" t="n">
-        <v>6360998.2766674</v>
+        <v>6361050</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +833,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Ardre</t>
+          <t>Alskog</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -878,110 +841,86 @@
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Tony Svensson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97969891</v>
+        <v>96511038</v>
       </c>
       <c r="B4" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220686</v>
+        <v>473</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>Bon</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hallute backe, 350 m SSO om, Gtl</t>
+          <t>Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>722265.6656659211</v>
+        <v>722260</v>
       </c>
       <c r="R4" t="n">
-        <v>6360985.855741367</v>
+        <v>6361047</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,27 +939,17 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Ardre</t>
+          <t>Alskog</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-01-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-01-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,81 +958,79 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Dennis Nyström, Peter Nilsson, Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127888821</v>
+        <v>97694548</v>
       </c>
       <c r="B5" t="n">
-        <v>56620</v>
+        <v>100666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100053</v>
+        <v>783</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lantmannavägen, 623 65 Ljugarn, Gtl</t>
+          <t>Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>722296</v>
+        <v>722275</v>
       </c>
       <c r="R5" t="n">
-        <v>6360820</v>
+        <v>6360998</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1127,22 +1054,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:31</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:31</t>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,25 +1073,368 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127888821</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56845</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lantmannavägen, 623 65 Ljugarn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>722296</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6360820</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Johan Möller</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Johan Möller</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96511035</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lauritse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>722263</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6360984</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Minst 50 plantor</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>97969891</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hallute backe, 350 m SSO om, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>722266</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6360986</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-01-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-01-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 73144-2021 artfynd.xlsx
+++ b/artfynd/A 73144-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96486085</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
           <t>SMF:s mykologivecka</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96511036</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96511038</t>
         </is>
       </c>
     </row>
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97694548</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127888821</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1325,6 +1355,11 @@
           <t>SMF:s mykologivecka</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96511035</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,8 +1470,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97969891</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>